--- a/Initial_incidence_map_tallies.xlsx
+++ b/Initial_incidence_map_tallies.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20382"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\showalt_d\Documents\GitHub\Apiary_LRR\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AEBBE6-F484-4F32-804F-EED16D2B5859}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="All_TRT" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="ABC" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="All_TRT" sheetId="1" r:id="rId1"/>
+    <sheet name="ABC" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -23,212 +28,184 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="57">
   <si>
-    <t xml:space="preserve">TMT</t>
+    <t>TMT</t>
   </si>
   <si>
-    <t xml:space="preserve">STAND</t>
+    <t>STAND</t>
   </si>
   <si>
-    <t xml:space="preserve">SEVERITY</t>
+    <t>SEVERITY</t>
   </si>
   <si>
-    <t xml:space="preserve">NAME</t>
+    <t>NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">PLOT</t>
+    <t>PLOT</t>
   </si>
   <si>
-    <t xml:space="preserve">diamond</t>
+    <t>diamond</t>
   </si>
   <si>
-    <t xml:space="preserve">--</t>
+    <t>--</t>
   </si>
   <si>
-    <t xml:space="preserve">|</t>
+    <t>|</t>
   </si>
   <si>
-    <t xml:space="preserve">+</t>
+    <t>+</t>
   </si>
   <si>
-    <t xml:space="preserve">x</t>
+    <t>x</t>
   </si>
   <si>
-    <t xml:space="preserve">?</t>
+    <t>?</t>
   </si>
   <si>
-    <t xml:space="preserve">Poria, old stump</t>
+    <t>Poria, old stump</t>
   </si>
   <si>
-    <t xml:space="preserve">Poria, dead &gt;10Y</t>
+    <t>Poria, dead &gt;10Y</t>
   </si>
   <si>
-    <t xml:space="preserve">Poria, dead &lt;10Y</t>
+    <t>Poria, dead &lt;10Y</t>
   </si>
   <si>
-    <t xml:space="preserve">Poria, alive, symptoms</t>
+    <t>Poria, alive, symptoms</t>
   </si>
   <si>
-    <t xml:space="preserve">Poria, alive, stump detection</t>
+    <t>Poria, alive, stump detection</t>
   </si>
   <si>
-    <t xml:space="preserve">dead, unknown (ARM)</t>
+    <t>dead, unknown (ARM)</t>
   </si>
   <si>
-    <t xml:space="preserve">poria sum</t>
+    <t>poria sum</t>
   </si>
   <si>
-    <t xml:space="preserve">not old stump</t>
+    <t>not old stump</t>
   </si>
   <si>
-    <t xml:space="preserve">&gt;10Y</t>
+    <t>&gt;10Y</t>
   </si>
   <si>
-    <t xml:space="preserve">poria rank</t>
+    <t>poria rank</t>
   </si>
   <si>
-    <t xml:space="preserve">not old stump rank</t>
+    <t>not old stump rank</t>
   </si>
   <si>
-    <t xml:space="preserve">&gt;10Y rank</t>
+    <t>&gt;10Y rank</t>
   </si>
   <si>
-    <t xml:space="preserve">Stand ave poria rank</t>
+    <t>Stand ave poria rank</t>
   </si>
   <si>
-    <t xml:space="preserve">Stand ave not old stump rank</t>
+    <t>Stand ave not old stump rank</t>
   </si>
   <si>
-    <t xml:space="preserve">Stand ave &gt;10Y rank</t>
+    <t>Stand ave &gt;10Y rank</t>
   </si>
   <si>
-    <t xml:space="preserve">A</t>
+    <t>A</t>
   </si>
   <si>
-    <t xml:space="preserve">A1</t>
+    <t>A1</t>
   </si>
   <si>
-    <t xml:space="preserve">B</t>
+    <t>B</t>
   </si>
   <si>
-    <t xml:space="preserve">B1</t>
+    <t>B1</t>
   </si>
   <si>
-    <t xml:space="preserve">C</t>
+    <t>C</t>
   </si>
   <si>
-    <t xml:space="preserve">C1</t>
+    <t>C1</t>
   </si>
   <si>
-    <t xml:space="preserve">D</t>
+    <t>D</t>
   </si>
   <si>
-    <t xml:space="preserve">D1</t>
+    <t>D1</t>
   </si>
   <si>
-    <t xml:space="preserve">E</t>
+    <t>E</t>
   </si>
   <si>
-    <t xml:space="preserve">E1</t>
+    <t>E1</t>
   </si>
   <si>
-    <t xml:space="preserve">A2</t>
+    <t>A2</t>
   </si>
   <si>
-    <t xml:space="preserve">B2</t>
+    <t>B2</t>
   </si>
   <si>
-    <t xml:space="preserve">C2</t>
+    <t>C2</t>
   </si>
   <si>
-    <t xml:space="preserve">D2</t>
+    <t>D2</t>
   </si>
   <si>
-    <t xml:space="preserve">E2</t>
+    <t>E2</t>
   </si>
   <si>
-    <t xml:space="preserve">A3</t>
+    <t>A3</t>
   </si>
   <si>
-    <t xml:space="preserve">B3</t>
+    <t>B3</t>
   </si>
   <si>
-    <t xml:space="preserve">C3</t>
+    <t>C3</t>
   </si>
   <si>
-    <t xml:space="preserve">D3</t>
+    <t>D3</t>
   </si>
   <si>
-    <t xml:space="preserve">E3</t>
+    <t>E3</t>
   </si>
   <si>
-    <t xml:space="preserve">A4</t>
+    <t>A4</t>
   </si>
   <si>
-    <t xml:space="preserve">B4</t>
+    <t>B4</t>
   </si>
   <si>
-    <t xml:space="preserve">C4</t>
+    <t>C4</t>
   </si>
   <si>
-    <t xml:space="preserve">D4</t>
+    <t>D4</t>
   </si>
   <si>
-    <t xml:space="preserve">E4</t>
+    <t>E4</t>
   </si>
   <si>
-    <t xml:space="preserve">A0</t>
+    <t>A0</t>
   </si>
   <si>
-    <t xml:space="preserve">B0</t>
+    <t>B0</t>
   </si>
   <si>
-    <t xml:space="preserve">C0</t>
+    <t>C0</t>
   </si>
   <si>
-    <t xml:space="preserve">D0</t>
+    <t>D0</t>
   </si>
   <si>
-    <t xml:space="preserve">E0</t>
+    <t>E0</t>
   </si>
   <si>
-    <t xml:space="preserve">condition sum</t>
+    <t>condition sum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -284,7 +261,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -292,105 +269,60 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -449,15 +381,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -466,12 +416,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr sz="1300" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr lang="en-US" sz="1300" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Pre-harvest laminated root rot incidence</a:t>
@@ -489,6 +439,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
@@ -517,15 +468,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -533,8 +492,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -708,6 +668,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8C8D-4D13-AE47-6C27B50997A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -725,7 +690,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff0000"/>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -733,15 +698,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -749,8 +722,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -924,6 +898,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8C8D-4D13-AE47-6C27B50997A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -941,7 +920,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffbf00"/>
+              <a:srgbClr val="FFBF00"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -949,15 +928,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -965,8 +952,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1140,6 +1128,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8C8D-4D13-AE47-6C27B50997A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1157,7 +1150,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2a6099"/>
+              <a:srgbClr val="2A6099"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1165,15 +1158,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1181,8 +1182,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1356,6 +1358,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8C8D-4D13-AE47-6C27B50997A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -1373,7 +1380,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="00a933"/>
+              <a:srgbClr val="00A933"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1381,15 +1388,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1397,8 +1412,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1572,7 +1588,20 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-8C8D-4D13-AE47-6C27B50997A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
         <c:axId val="6312028"/>
@@ -1592,12 +1621,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:rPr>
                   <a:t>Plots</a:t>
@@ -1620,7 +1649,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1629,10 +1658,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="19870359"/>
@@ -1653,7 +1683,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1665,12 +1695,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:rPr>
                   <a:t>Trees</a:t>
@@ -1693,7 +1723,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1702,10 +1732,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="6312028"/>
@@ -1716,7 +1747,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
+            <a:srgbClr val="B3B3B3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -1735,31 +1766,40 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1768,12 +1808,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr sz="1300" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr lang="en-US" sz="1300" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Pre-harvest laminated root rot incidence</a:t>
@@ -1791,6 +1831,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
@@ -1819,15 +1860,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1835,8 +1884,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1950,6 +2000,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-06EF-439C-AC7D-D8D92D745C9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1967,7 +2022,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff0000"/>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1975,15 +2030,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1991,8 +2054,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2106,6 +2170,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-06EF-439C-AC7D-D8D92D745C9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2123,7 +2192,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffbf00"/>
+              <a:srgbClr val="FFBF00"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -2131,15 +2200,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2147,8 +2224,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2262,6 +2340,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-06EF-439C-AC7D-D8D92D745C9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -2279,7 +2362,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2a6099"/>
+              <a:srgbClr val="2A6099"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -2287,15 +2370,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2303,8 +2394,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2418,6 +2510,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-06EF-439C-AC7D-D8D92D745C9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -2435,7 +2532,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="00a933"/>
+              <a:srgbClr val="00A933"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -2443,15 +2540,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2459,8 +2564,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2574,7 +2680,20 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-06EF-439C-AC7D-D8D92D745C9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
         <c:axId val="30548539"/>
@@ -2594,12 +2713,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:rPr>
                   <a:t>Plots</a:t>
@@ -2622,7 +2741,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -2631,10 +2750,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="46987352"/>
@@ -2655,7 +2775,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -2667,12 +2787,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:defRPr sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="900" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:rPr>
                   <a:t>Trees</a:t>
@@ -2695,7 +2815,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -2704,10 +2824,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="30548539"/>
@@ -2718,7 +2839,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
+            <a:srgbClr val="B3B3B3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -2737,29 +2858,36 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -2773,14 +2901,20 @@
       <xdr:row>64</xdr:row>
       <xdr:rowOff>25560</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="1203840" y="5127480"/>
-        <a:ext cx="10031040" cy="5584320"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2803,9 +2937,15 @@
       <xdr:row>60</xdr:row>
       <xdr:rowOff>5040</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2818,14 +2958,20 @@
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -2844,9 +2990,15 @@
       <xdr:row>59</xdr:row>
       <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2859,14 +3011,20 @@
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -2885,9 +3043,15 @@
       <xdr:row>60</xdr:row>
       <xdr:rowOff>33120</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvPr id="5" name="Straight Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2900,14 +3064,20 @@
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -2926,9 +3096,15 @@
       <xdr:row>60</xdr:row>
       <xdr:rowOff>5040</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvPr id="6" name="Straight Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2941,14 +3117,20 @@
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -2958,7 +3140,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -2972,14 +3154,20 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>95040</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name=""/>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="957240" y="3444480"/>
-        <a:ext cx="7943400" cy="4422240"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2992,39 +3180,51 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>611280</xdr:colOff>
+      <xdr:colOff>432955</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>144360</xdr:rowOff>
+      <xdr:rowOff>8660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>629280</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>89640</xdr:rowOff>
+      <xdr:colOff>447439</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>55005</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name=""/>
+        <xdr:cNvPr id="6" name="Straight Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2740320" y="4014360"/>
-          <a:ext cx="18000" cy="3196800"/>
+          <a:off x="2459182" y="4113069"/>
+          <a:ext cx="14484" cy="3501322"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -3033,39 +3233,51 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>810000</xdr:colOff>
+      <xdr:colOff>650672</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>118440</xdr:rowOff>
+      <xdr:rowOff>23192</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>27000</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>107640</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>684069</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name=""/>
+        <xdr:cNvPr id="7" name="Straight Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3751920" y="3988440"/>
-          <a:ext cx="29520" cy="3240720"/>
+          <a:off x="3447558" y="4127601"/>
+          <a:ext cx="33397" cy="3501058"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -3074,39 +3286,51 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>217800</xdr:colOff>
+      <xdr:colOff>96573</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>144720</xdr:rowOff>
+      <xdr:rowOff>14835</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>234720</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:colOff>121226</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>86591</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name=""/>
+        <xdr:cNvPr id="8" name="Straight Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4784760" y="4014720"/>
-          <a:ext cx="16920" cy="3205440"/>
+          <a:off x="4434778" y="4119244"/>
+          <a:ext cx="24653" cy="3526733"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -3115,39 +3339,51 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>441000</xdr:colOff>
+      <xdr:colOff>346363</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>144720</xdr:rowOff>
+      <xdr:rowOff>14835</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>447120</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>116640</xdr:rowOff>
+      <xdr:colOff>351871</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>51955</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name=""/>
+        <xdr:cNvPr id="9" name="Straight Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5820840" y="4014720"/>
-          <a:ext cx="6120" cy="3223440"/>
+          <a:off x="5455227" y="4119244"/>
+          <a:ext cx="5508" cy="3492097"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="3465a4"/>
+            <a:srgbClr val="3465A4"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="minor"/>
       </xdr:style>
     </xdr:sp>
@@ -3156,29 +3392,321 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AMJ29"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="5.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="4.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="5.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8.84"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="11" max="11" width="5.28515625" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" customWidth="1"/>
+    <col min="16" max="16" width="5.42578125" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3199,7 +3727,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3223,7 +3751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:1024" s="8" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="E3" s="9" t="s">
         <v>11</v>
       </c>
@@ -3269,1347 +3797,1347 @@
       <c r="S3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AMJ3" s="0"/>
+      <c r="AMJ3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>6</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4">
         <v>6</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="n">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>14</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4">
         <v>14</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4">
         <v>8</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4">
         <v>23</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4">
         <v>22</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4">
         <v>22</v>
       </c>
-      <c r="Q4" s="0" t="n">
-        <f aca="false">AVERAGE(N4:N8)</f>
+      <c r="Q4">
+        <f>AVERAGE(N4:N8)</f>
         <v>22.8</v>
       </c>
-      <c r="R4" s="0" t="n">
-        <f aca="false">AVERAGE(O4:O8)</f>
+      <c r="R4">
+        <f>AVERAGE(O4:O8)</f>
         <v>22.2</v>
       </c>
-      <c r="S4" s="0" t="n">
-        <f aca="false">AVERAGE(P4:P8)</f>
+      <c r="S4">
+        <f>AVERAGE(P4:P8)</f>
         <v>20.8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0" t="n">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>8</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="n">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>13</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5">
         <v>12</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5">
         <v>8</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5">
         <v>24</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5">
         <v>24</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5">
         <v>22</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>9</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="n">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>15</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6">
         <v>15</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6">
         <v>14</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6">
         <v>21</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6">
         <v>20</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6">
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7">
         <v>3</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="15">
         <v>4</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7">
         <v>12</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7">
         <v>11</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7">
         <v>8</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7">
         <v>25</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7">
         <v>25</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7">
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="0" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8">
         <v>4</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>5</v>
       </c>
-      <c r="J8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="n">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>15</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8">
         <v>15</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8">
         <v>9</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8">
         <v>21</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8">
         <v>20</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8">
         <v>21</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>6</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9">
         <v>8</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="n">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>26</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9">
         <v>26</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9">
         <v>20</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9">
         <v>17</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9">
         <v>16</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9">
         <v>9</v>
       </c>
-      <c r="Q9" s="0" t="n">
-        <f aca="false">AVERAGE(N9:N13)</f>
-        <v>17.6</v>
-      </c>
-      <c r="R9" s="0" t="n">
-        <f aca="false">AVERAGE(O9:O13)</f>
-        <v>18.4</v>
-      </c>
-      <c r="S9" s="0" t="n">
-        <f aca="false">AVERAGE(P9:P13)</f>
+      <c r="Q9">
+        <f>AVERAGE(N9:N13)</f>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="R9">
+        <f>AVERAGE(O9:O13)</f>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="S9">
+        <f>AVERAGE(P9:P13)</f>
         <v>17.8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>6</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10">
         <v>7</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0" t="n">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>6</v>
       </c>
-      <c r="J10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="n">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>19</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10">
         <v>19</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10">
         <v>13</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10">
         <v>19</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10">
         <v>19</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11">
         <v>12</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11">
         <v>9</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="J11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="n">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>28</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11">
         <v>26</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11">
         <v>14</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11">
         <v>14</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11">
         <v>16</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0" t="n">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>7</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12">
         <v>6</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="0" t="n">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>7</v>
       </c>
-      <c r="J12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="n">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>20</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12">
         <v>20</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12">
         <v>13</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12">
         <v>18</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12">
         <v>18</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13">
         <v>2</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13">
         <v>4</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13">
         <v>7</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13">
         <v>3</v>
       </c>
-      <c r="H13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="0" t="n">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>3</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="15">
         <v>2</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13">
         <v>17</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13">
         <v>13</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13">
         <v>6</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13">
         <v>20</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13">
         <v>23</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="P13">
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14">
         <v>3</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="0" t="n">
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>12</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14">
         <v>9</v>
       </c>
-      <c r="H14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="0" t="n">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>7</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="15">
         <v>1</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14">
         <v>28</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14">
         <v>28</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14">
         <v>16</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14">
         <v>14</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14">
         <v>13</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14">
         <v>13</v>
       </c>
-      <c r="Q14" s="0" t="n">
-        <f aca="false">AVERAGE(N14:N18)</f>
+      <c r="Q14">
+        <f>AVERAGE(N14:N18)</f>
         <v>12.6</v>
       </c>
-      <c r="R14" s="0" t="n">
-        <f aca="false">AVERAGE(O14:O18)</f>
+      <c r="R14">
+        <f>AVERAGE(O14:O18)</f>
         <v>12.6</v>
       </c>
-      <c r="S14" s="0" t="n">
-        <f aca="false">AVERAGE(P14:P18)</f>
+      <c r="S14">
+        <f>AVERAGE(P14:P18)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15">
         <v>3</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15">
         <v>3</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="0" t="n">
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>10</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15">
         <v>10</v>
       </c>
-      <c r="H15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="0" t="n">
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="15">
         <v>1</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15">
         <v>30</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15">
         <v>30</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15">
         <v>20</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15">
         <v>12</v>
       </c>
-      <c r="O15" s="0" t="n">
+      <c r="O15">
         <v>12</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16">
         <v>3</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16">
         <v>12</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16">
         <v>10</v>
       </c>
-      <c r="H16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="0" t="n">
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>6</v>
       </c>
-      <c r="J16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="n">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>29</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16">
         <v>28</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16">
         <v>16</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16">
         <v>13</v>
       </c>
-      <c r="O16" s="0" t="n">
+      <c r="O16">
         <v>13</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17">
         <v>3</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17">
         <v>3</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17">
         <v>11</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17">
         <v>9</v>
       </c>
-      <c r="H17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="0" t="n">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>11</v>
       </c>
-      <c r="J17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="0" t="n">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>32</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17">
         <v>31</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17">
         <v>20</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17">
         <v>10</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17">
         <v>10</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17">
         <v>9</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18">
         <v>3</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18">
         <v>3</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18">
         <v>12</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18">
         <v>4</v>
       </c>
-      <c r="H18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="0" t="n">
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>11</v>
       </c>
-      <c r="J18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0" t="n">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>28</v>
       </c>
-      <c r="L18" s="0" t="n">
+      <c r="L18">
         <v>27</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18">
         <v>15</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18">
         <v>14</v>
       </c>
-      <c r="O18" s="0" t="n">
+      <c r="O18">
         <v>15</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19">
         <v>4</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19">
         <v>4</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19">
         <v>3</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19">
         <v>10</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19">
         <v>14</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19">
         <v>2</v>
       </c>
-      <c r="I19" s="0" t="n">
+      <c r="I19">
         <v>20</v>
       </c>
-      <c r="J19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0" t="n">
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
         <v>49</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19">
         <v>46</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19">
         <v>36</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19">
         <v>3</v>
       </c>
-      <c r="O19" s="0" t="n">
+      <c r="O19">
         <v>3</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="P19">
         <v>2</v>
       </c>
-      <c r="Q19" s="0" t="n">
-        <f aca="false">AVERAGE(N19:N23)</f>
+      <c r="Q19">
+        <f>AVERAGE(N19:N23)</f>
         <v>3.8</v>
       </c>
-      <c r="R19" s="0" t="n">
-        <f aca="false">AVERAGE(O19:O23)</f>
+      <c r="R19">
+        <f>AVERAGE(O19:O23)</f>
         <v>3.6</v>
       </c>
-      <c r="S19" s="0" t="n">
-        <f aca="false">AVERAGE(P19:P23)</f>
+      <c r="S19">
+        <f>AVERAGE(P19:P23)</f>
         <v>4.8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20">
         <v>4</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20">
         <v>19</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20">
         <v>9</v>
       </c>
-      <c r="H20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="0" t="n">
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>7</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="15">
         <v>3</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20">
         <v>36</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20">
         <v>35</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20">
         <v>16</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20">
         <v>8</v>
       </c>
-      <c r="O20" s="0" t="n">
+      <c r="O20">
         <v>8</v>
       </c>
-      <c r="P20" s="0" t="n">
+      <c r="P20">
         <v>13</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21">
         <v>4</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21">
         <v>4</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21">
         <v>6</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21">
         <v>14</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21">
         <v>10</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21">
         <v>2</v>
       </c>
-      <c r="I21" s="0" t="n">
+      <c r="I21">
         <v>28</v>
       </c>
-      <c r="J21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="0" t="n">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
         <v>60</v>
       </c>
-      <c r="L21" s="0" t="n">
+      <c r="L21">
         <v>54</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21">
         <v>40</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21">
         <v>2</v>
       </c>
-      <c r="O21" s="0" t="n">
+      <c r="O21">
         <v>2</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="P21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22">
         <v>4</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22">
         <v>2</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22">
         <v>42</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22">
         <v>12</v>
       </c>
-      <c r="H22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="0" t="n">
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>13</v>
       </c>
-      <c r="J22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="0" t="n">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
         <v>69</v>
       </c>
-      <c r="L22" s="0" t="n">
+      <c r="L22">
         <v>67</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22">
         <v>25</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22">
         <v>1</v>
       </c>
-      <c r="O22" s="0" t="n">
+      <c r="O22">
         <v>1</v>
       </c>
-      <c r="P22" s="0" t="n">
+      <c r="P22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23">
         <v>4</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="0" t="n">
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>10</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23">
         <v>15</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23">
         <v>1</v>
       </c>
-      <c r="I23" s="0" t="n">
+      <c r="I23">
         <v>19</v>
       </c>
-      <c r="J23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="0" t="n">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>45</v>
       </c>
-      <c r="L23" s="0" t="n">
+      <c r="L23">
         <v>45</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23">
         <v>35</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23">
         <v>5</v>
       </c>
-      <c r="O23" s="0" t="n">
+      <c r="O23">
         <v>4</v>
       </c>
-      <c r="P23" s="0" t="n">
+      <c r="P23">
         <v>3</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="0" t="n">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>5</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24">
         <v>2</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24">
         <v>17</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24">
         <v>13</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="I24">
         <v>12</v>
       </c>
-      <c r="J24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="0" t="n">
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>46</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="L24">
         <v>44</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24">
         <v>27</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24">
         <v>4</v>
       </c>
-      <c r="O24" s="0" t="n">
+      <c r="O24">
         <v>5</v>
       </c>
-      <c r="P24" s="0" t="n">
+      <c r="P24">
         <v>4</v>
       </c>
-      <c r="Q24" s="0" t="n">
-        <f aca="false">AVERAGE(N24:N28)</f>
+      <c r="Q24">
+        <f>AVERAGE(N24:N28)</f>
         <v>7.4</v>
       </c>
-      <c r="R24" s="0" t="n">
-        <f aca="false">AVERAGE(O24:O28)</f>
+      <c r="R24">
+        <f>AVERAGE(O24:O28)</f>
         <v>7.4</v>
       </c>
-      <c r="S24" s="0" t="n">
-        <f aca="false">AVERAGE(P24:P28)</f>
+      <c r="S24">
+        <f>AVERAGE(P24:P28)</f>
         <v>6.8</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="0" t="n">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>5</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="0" t="n">
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>19</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25">
         <v>18</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25" s="0" t="n">
+      <c r="I25">
         <v>5</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="J25" s="15">
         <v>1</v>
       </c>
-      <c r="K25" s="0" t="n">
+      <c r="K25">
         <v>43</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25">
         <v>43</v>
       </c>
-      <c r="M25" s="0" t="n">
+      <c r="M25">
         <v>24</v>
       </c>
-      <c r="N25" s="0" t="n">
+      <c r="N25">
         <v>6</v>
       </c>
-      <c r="O25" s="0" t="n">
+      <c r="O25">
         <v>6</v>
       </c>
-      <c r="P25" s="0" t="n">
+      <c r="P25">
         <v>8</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="0" t="n">
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
         <v>5</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="0" t="n">
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>13</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26">
         <v>4</v>
       </c>
-      <c r="H26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="0" t="n">
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>14</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="15">
         <v>2</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="K26">
         <v>31</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26">
         <v>31</v>
       </c>
-      <c r="M26" s="0" t="n">
+      <c r="M26">
         <v>18</v>
       </c>
-      <c r="N26" s="0" t="n">
+      <c r="N26">
         <v>11</v>
       </c>
-      <c r="O26" s="0" t="n">
+      <c r="O26">
         <v>10</v>
       </c>
-      <c r="P26" s="0" t="n">
+      <c r="P26">
         <v>12</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="0" t="n">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
         <v>5</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="0" t="n">
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <v>8</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27">
         <v>12</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27">
         <v>2</v>
       </c>
-      <c r="I27" s="0" t="n">
+      <c r="I27">
         <v>11</v>
       </c>
-      <c r="J27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="0" t="n">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <v>33</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27">
         <v>33</v>
       </c>
-      <c r="M27" s="0" t="n">
+      <c r="M27">
         <v>25</v>
       </c>
-      <c r="N27" s="0" t="n">
+      <c r="N27">
         <v>9</v>
       </c>
-      <c r="O27" s="0" t="n">
+      <c r="O27">
         <v>9</v>
       </c>
-      <c r="P27" s="0" t="n">
+      <c r="P27">
         <v>5</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="0" t="n">
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
         <v>5</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28">
         <v>2</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28">
         <v>14</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28">
         <v>14</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28">
         <v>1</v>
       </c>
-      <c r="I28" s="0" t="n">
+      <c r="I28">
         <v>10</v>
       </c>
-      <c r="J28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="0" t="n">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
         <v>41</v>
       </c>
-      <c r="L28" s="0" t="n">
+      <c r="L28">
         <v>39</v>
       </c>
-      <c r="M28" s="0" t="n">
+      <c r="M28">
         <v>25</v>
       </c>
-      <c r="N28" s="0" t="n">
+      <c r="N28">
         <v>7</v>
       </c>
-      <c r="O28" s="0" t="n">
+      <c r="O28">
         <v>7</v>
       </c>
-      <c r="P28" s="0" t="n">
+      <c r="P28">
         <v>5</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="0" t="s">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
         <v>56</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29">
         <v>27</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29">
         <v>281</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29">
         <v>215</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29">
         <v>12</v>
       </c>
-      <c r="I29" s="0" t="n">
+      <c r="I29">
         <v>244</v>
       </c>
-      <c r="J29" s="0" t="n">
+      <c r="J29">
         <v>14</v>
       </c>
-      <c r="K29" s="0" t="n">
+      <c r="K29">
         <v>779</v>
       </c>
-      <c r="L29" s="0" t="n">
+      <c r="L29">
         <v>752</v>
       </c>
-      <c r="M29" s="0" t="n">
+      <c r="M29">
         <v>471</v>
       </c>
     </row>
@@ -4621,10 +5149,9 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:I1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -4633,28 +5160,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AMJ19"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="5.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="5.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="5.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="10.22"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="11" max="11" width="5.140625" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" customWidth="1"/>
+    <col min="14" max="14" width="5" customWidth="1"/>
+    <col min="15" max="15" width="6.28515625" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4675,7 +5199,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4699,7 +5223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="true" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:1024" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="E3" s="9" t="s">
         <v>11</v>
       </c>
@@ -4745,832 +5269,832 @@
       <c r="S3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AMJ3" s="0"/>
+      <c r="AMJ3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>6</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4">
         <v>6</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="n">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>14</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4">
         <v>14</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4">
         <v>8</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4">
         <v>14</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4">
         <v>14</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4">
         <v>14</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4">
         <v>14</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4">
         <v>14</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4">
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0" t="n">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>8</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="n">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>13</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5">
         <v>12</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5">
         <v>8</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5">
         <v>15</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5">
         <v>15</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>9</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="n">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>15</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6">
         <v>15</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6">
         <v>14</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6">
         <v>13</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6">
         <v>13</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>6</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0" t="n">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="n">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>26</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7">
         <v>26</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7">
         <v>20</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7">
         <v>11</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7">
         <v>10</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7">
         <v>5</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7">
         <v>10.6666666666667</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7">
         <v>10.6666666666667</v>
       </c>
-      <c r="S7" s="0" t="n">
-        <v>9.66666666666667</v>
+      <c r="S7">
+        <v>9.6666666666666696</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="0" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8">
         <v>7</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>6</v>
       </c>
-      <c r="J8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="n">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>19</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8">
         <v>19</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8">
         <v>13</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8">
         <v>12</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8">
         <v>12</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8">
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9">
         <v>12</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9">
         <v>9</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="J9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="n">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>28</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9">
         <v>26</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9">
         <v>14</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9">
         <v>9</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9">
         <v>10</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9">
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>12</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10">
         <v>9</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0" t="n">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>7</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="15">
         <v>1</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10">
         <v>28</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10">
         <v>28</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10">
         <v>16</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10">
         <v>9</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10">
         <v>8</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10">
         <v>8</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="Q10">
         <v>8</v>
       </c>
-      <c r="R10" s="0" t="n">
-        <v>7.66666666666667</v>
-      </c>
-      <c r="S10" s="0" t="n">
+      <c r="R10">
+        <v>7.6666666666666696</v>
+      </c>
+      <c r="S10">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11">
         <v>3</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="n">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>10</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11">
         <v>10</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="15">
         <v>1</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11">
         <v>30</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11">
         <v>30</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11">
         <v>20</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11">
         <v>7</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11">
         <v>7</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12">
         <v>3</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12">
         <v>12</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12">
         <v>10</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="0" t="n">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>6</v>
       </c>
-      <c r="J12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="n">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>29</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12">
         <v>28</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12">
         <v>16</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12">
         <v>8</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12">
         <v>8</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13">
         <v>4</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13">
         <v>3</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13">
         <v>10</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13">
         <v>14</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="I13">
         <v>20</v>
       </c>
-      <c r="J13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0" t="n">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>49</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13">
         <v>46</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13">
         <v>36</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13">
         <v>2</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13">
         <v>2</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="P13">
         <v>2</v>
       </c>
-      <c r="Q13" s="0" t="n">
-        <v>2.66666666666667</v>
-      </c>
-      <c r="R13" s="0" t="n">
-        <v>2.66666666666667</v>
-      </c>
-      <c r="S13" s="0" t="n">
-        <v>3.66666666666667</v>
+      <c r="Q13">
+        <v>2.6666666666666701</v>
+      </c>
+      <c r="R13">
+        <v>2.6666666666666701</v>
+      </c>
+      <c r="S13">
+        <v>3.6666666666666701</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>4</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14">
         <v>19</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14">
         <v>9</v>
       </c>
-      <c r="H14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="0" t="n">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>7</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="15">
         <v>3</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14">
         <v>36</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14">
         <v>35</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14">
         <v>16</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14">
         <v>5</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14">
         <v>5</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14">
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15">
         <v>4</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15">
         <v>6</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15">
         <v>14</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15">
         <v>10</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15">
         <v>2</v>
       </c>
-      <c r="I15" s="0" t="n">
+      <c r="I15">
         <v>28</v>
       </c>
-      <c r="J15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0" t="n">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>60</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15">
         <v>54</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15">
         <v>40</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15">
         <v>1</v>
       </c>
-      <c r="O15" s="0" t="n">
+      <c r="O15">
         <v>1</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="0" t="n">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16">
         <v>17</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16">
         <v>13</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16">
         <v>2</v>
       </c>
-      <c r="I16" s="0" t="n">
+      <c r="I16">
         <v>12</v>
       </c>
-      <c r="J16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="n">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>46</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16">
         <v>44</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16">
         <v>27</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16">
         <v>3</v>
       </c>
-      <c r="O16" s="0" t="n">
+      <c r="O16">
         <v>3</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16">
         <v>3</v>
       </c>
-      <c r="Q16" s="0" t="n">
-        <v>4.33333333333333</v>
-      </c>
-      <c r="R16" s="0" t="n">
-        <v>4.33333333333333</v>
-      </c>
-      <c r="S16" s="0" t="n">
-        <v>4.66666666666667</v>
+      <c r="Q16">
+        <v>4.3333333333333304</v>
+      </c>
+      <c r="R16">
+        <v>4.3333333333333304</v>
+      </c>
+      <c r="S16">
+        <v>4.6666666666666696</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="0" t="n">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>5</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="0" t="n">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>19</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17">
         <v>18</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17">
         <v>1</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17">
         <v>5</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="15">
         <v>1</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17">
         <v>43</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17">
         <v>43</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17">
         <v>24</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17">
         <v>4</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17">
         <v>4</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17">
         <v>4</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="0" t="n">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>5</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="0" t="n">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>13</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18">
         <v>4</v>
       </c>
-      <c r="H18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="0" t="n">
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>14</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="15">
         <v>2</v>
       </c>
-      <c r="K18" s="0" t="n">
+      <c r="K18">
         <v>31</v>
       </c>
-      <c r="L18" s="0" t="n">
+      <c r="L18">
         <v>31</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18">
         <v>18</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18">
         <v>6</v>
       </c>
-      <c r="O18" s="0" t="n">
+      <c r="O18">
         <v>6</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18">
         <v>7</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="0" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19">
         <v>27</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19">
         <v>281</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19">
         <v>215</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19">
         <v>12</v>
       </c>
-      <c r="I19" s="0" t="n">
+      <c r="I19">
         <v>244</v>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J19">
         <v>14</v>
       </c>
-      <c r="K19" s="0" t="n">
+      <c r="K19">
         <v>779</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19">
         <v>752</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19">
         <v>471</v>
       </c>
     </row>
@@ -5582,10 +6106,9 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:I1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
